--- a/Result/profitability/5464.xlsx
+++ b/Result/profitability/5464.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.89</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2174999999999999</v>
+        <v>-0.1437499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>5.67625</v>
+        <v>6.74375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01874999999999992</v>
+        <v>-0.1599999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>7.9275</v>
+        <v>7.453749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.001249999999999918</v>
+        <v>-0.08499999999999992</v>
       </c>
       <c r="N4" t="n">
-        <v>8.7875</v>
+        <v>8.462499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08625000000000008</v>
+        <v>0.4862500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>10.37</v>
+        <v>11.06375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.5925</v>
       </c>
       <c r="N6" t="n">
-        <v>13.5375</v>
+        <v>15.2775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,13 +1264,13 @@
         <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7075</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>17.28125</v>
+        <v>17.785</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6975</v>
+        <v>0.6312500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>19.07375</v>
+        <v>19.5625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1518,7 +1518,7 @@
         <v>0.59</v>
       </c>
       <c r="M9" t="n">
-        <v>0.75125</v>
+        <v>0.7512500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>21.11625</v>
@@ -1772,7 +1772,7 @@
         <v>1.02</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7425</v>
+        <v>0.7425000000000002</v>
       </c>
       <c r="N11" t="n">
         <v>21.3925</v>
@@ -1899,7 +1899,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>21.39125</v>
@@ -2026,7 +2026,7 @@
         <v>-0.79</v>
       </c>
       <c r="M13" t="n">
-        <v>0.47625</v>
+        <v>0.4762500000000001</v>
       </c>
       <c r="N13" t="n">
         <v>20.15625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5464</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>327</v>
+      </c>
+      <c r="D75" t="n">
+        <v>300</v>
+      </c>
+      <c r="E75" t="n">
+        <v>27</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.39%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3749999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.3125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.909999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.8967889908256879</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.896358543417367</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.549999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.040441176470588</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
